--- a/schedule-report-template.xlsx
+++ b/schedule-report-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p\Desktop\검사부 스켸줄러\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F4975-8137-4AFE-B765-A5F551AFD9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F4B6A-B655-4DC8-97DA-B1616B322897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 취합 (야간근무+연장)" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3083,7 +3083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3333,23 +3333,35 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3381,35 +3393,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4288,20 +4294,20 @@
       <c r="BB1" s="6"/>
     </row>
     <row r="2" spans="1:66" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="A2" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
       <c r="AT2" s="5"/>
       <c r="AU2" s="5"/>
       <c r="AV2" s="5"/>
@@ -4315,41 +4321,41 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="101" t="s">
+      <c r="B3" s="84"/>
+      <c r="C3" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="103">
+      <c r="D3" s="84"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="87">
         <v>6</v>
       </c>
-      <c r="G3" s="104"/>
+      <c r="G3" s="88"/>
       <c r="H3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="105" t="s">
+      <c r="I3" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="106"/>
-      <c r="K3" s="107">
+      <c r="J3" s="90"/>
+      <c r="K3" s="91">
         <v>25</v>
       </c>
-      <c r="L3" s="108"/>
+      <c r="L3" s="92"/>
       <c r="M3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="89" t="s">
+      <c r="N3" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="90"/>
-      <c r="P3" s="91">
+      <c r="O3" s="94"/>
+      <c r="P3" s="95">
         <v>18</v>
       </c>
-      <c r="Q3" s="92"/>
+      <c r="Q3" s="96"/>
       <c r="R3" s="9" t="s">
         <v>6</v>
       </c>
@@ -4364,32 +4370,32 @@
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
-      <c r="AD3" s="93" t="s">
+      <c r="AD3" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="93"/>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="93"/>
-      <c r="AL3" s="93"/>
-      <c r="AM3" s="93"/>
-      <c r="AN3" s="93"/>
-      <c r="AO3" s="93"/>
-      <c r="AP3" s="93"/>
-      <c r="AQ3" s="93"/>
-      <c r="AR3" s="93"/>
-      <c r="AS3" s="93"/>
-      <c r="AT3" s="93"/>
-      <c r="AU3" s="93"/>
-      <c r="AV3" s="93"/>
-      <c r="AW3" s="93"/>
-      <c r="AX3" s="93"/>
-      <c r="AY3" s="93"/>
-      <c r="AZ3" s="93"/>
-      <c r="BA3" s="93"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="97"/>
+      <c r="AI3" s="97"/>
+      <c r="AJ3" s="97"/>
+      <c r="AK3" s="97"/>
+      <c r="AL3" s="97"/>
+      <c r="AM3" s="97"/>
+      <c r="AN3" s="97"/>
+      <c r="AO3" s="97"/>
+      <c r="AP3" s="97"/>
+      <c r="AQ3" s="97"/>
+      <c r="AR3" s="97"/>
+      <c r="AS3" s="97"/>
+      <c r="AT3" s="97"/>
+      <c r="AU3" s="97"/>
+      <c r="AV3" s="97"/>
+      <c r="AW3" s="97"/>
+      <c r="AX3" s="97"/>
+      <c r="AY3" s="97"/>
+      <c r="AZ3" s="97"/>
+      <c r="BA3" s="97"/>
     </row>
     <row r="4" spans="1:66" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="12"/>
@@ -4443,53 +4449,53 @@
       <c r="BB4" s="15"/>
     </row>
     <row r="5" spans="1:66" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97" t="s">
+      <c r="G5" s="101"/>
+      <c r="H5" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97" t="s">
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97" t="s">
+      <c r="N5" s="101"/>
+      <c r="O5" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97" t="s">
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="97"/>
-      <c r="V5" s="97" t="s">
+      <c r="U5" s="101"/>
+      <c r="V5" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="97"/>
-      <c r="X5" s="97"/>
-      <c r="Y5" s="97"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="86"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="88"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
+      <c r="W5" s="101"/>
+      <c r="X5" s="101"/>
+      <c r="Y5" s="101"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="107"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="107"/>
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="107"/>
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
@@ -8375,102 +8381,87 @@
       <c r="BC40" s="70"/>
     </row>
     <row r="52" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD52" s="83"/>
-      <c r="BE52" s="83"/>
-      <c r="BF52" s="83"/>
-      <c r="BG52" s="83"/>
-      <c r="BH52" s="83"/>
-      <c r="BI52" s="83"/>
-      <c r="BJ52" s="83"/>
-      <c r="BK52" s="83"/>
-      <c r="BL52" s="83"/>
-      <c r="BM52" s="83"/>
-      <c r="BN52" s="83"/>
-      <c r="BO52" s="83"/>
-      <c r="BP52" s="83"/>
-      <c r="BQ52" s="83"/>
+      <c r="BD52" s="103"/>
+      <c r="BE52" s="103"/>
+      <c r="BF52" s="103"/>
+      <c r="BG52" s="103"/>
+      <c r="BH52" s="103"/>
+      <c r="BI52" s="103"/>
+      <c r="BJ52" s="103"/>
+      <c r="BK52" s="103"/>
+      <c r="BL52" s="103"/>
+      <c r="BM52" s="103"/>
+      <c r="BN52" s="103"/>
+      <c r="BO52" s="103"/>
+      <c r="BP52" s="103"/>
+      <c r="BQ52" s="103"/>
     </row>
     <row r="53" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD53" s="84"/>
-      <c r="BE53" s="84"/>
-      <c r="BF53" s="84"/>
-      <c r="BG53" s="84"/>
-      <c r="BH53" s="84"/>
-      <c r="BI53" s="84"/>
-      <c r="BJ53" s="84"/>
-      <c r="BK53" s="84"/>
-      <c r="BL53" s="84"/>
-      <c r="BM53" s="84"/>
-      <c r="BN53" s="84"/>
-      <c r="BO53" s="84"/>
-      <c r="BP53" s="84"/>
-      <c r="BQ53" s="84"/>
+      <c r="BD53" s="104"/>
+      <c r="BE53" s="104"/>
+      <c r="BF53" s="104"/>
+      <c r="BG53" s="104"/>
+      <c r="BH53" s="104"/>
+      <c r="BI53" s="104"/>
+      <c r="BJ53" s="104"/>
+      <c r="BK53" s="104"/>
+      <c r="BL53" s="104"/>
+      <c r="BM53" s="104"/>
+      <c r="BN53" s="104"/>
+      <c r="BO53" s="104"/>
+      <c r="BP53" s="104"/>
+      <c r="BQ53" s="104"/>
     </row>
     <row r="54" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD54" s="84"/>
-      <c r="BE54" s="84"/>
-      <c r="BF54" s="84"/>
-      <c r="BG54" s="84"/>
-      <c r="BH54" s="84"/>
-      <c r="BI54" s="84"/>
-      <c r="BJ54" s="84"/>
-      <c r="BK54" s="84"/>
-      <c r="BL54" s="84"/>
-      <c r="BM54" s="84"/>
-      <c r="BN54" s="84"/>
-      <c r="BO54" s="84"/>
-      <c r="BP54" s="84"/>
-      <c r="BQ54" s="84"/>
+      <c r="BD54" s="104"/>
+      <c r="BE54" s="104"/>
+      <c r="BF54" s="104"/>
+      <c r="BG54" s="104"/>
+      <c r="BH54" s="104"/>
+      <c r="BI54" s="104"/>
+      <c r="BJ54" s="104"/>
+      <c r="BK54" s="104"/>
+      <c r="BL54" s="104"/>
+      <c r="BM54" s="104"/>
+      <c r="BN54" s="104"/>
+      <c r="BO54" s="104"/>
+      <c r="BP54" s="104"/>
+      <c r="BQ54" s="104"/>
     </row>
     <row r="55" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD55" s="84"/>
-      <c r="BE55" s="84"/>
-      <c r="BF55" s="84"/>
-      <c r="BG55" s="84"/>
-      <c r="BH55" s="84"/>
-      <c r="BI55" s="84"/>
-      <c r="BJ55" s="84"/>
-      <c r="BK55" s="84"/>
-      <c r="BL55" s="84"/>
-      <c r="BM55" s="84"/>
-      <c r="BN55" s="84"/>
-      <c r="BO55" s="84"/>
-      <c r="BP55" s="84"/>
-      <c r="BQ55" s="84"/>
+      <c r="BD55" s="104"/>
+      <c r="BE55" s="104"/>
+      <c r="BF55" s="104"/>
+      <c r="BG55" s="104"/>
+      <c r="BH55" s="104"/>
+      <c r="BI55" s="104"/>
+      <c r="BJ55" s="104"/>
+      <c r="BK55" s="104"/>
+      <c r="BL55" s="104"/>
+      <c r="BM55" s="104"/>
+      <c r="BN55" s="104"/>
+      <c r="BO55" s="104"/>
+      <c r="BP55" s="104"/>
+      <c r="BQ55" s="104"/>
     </row>
     <row r="56" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD56" s="85"/>
-      <c r="BE56" s="85"/>
-      <c r="BF56" s="85"/>
-      <c r="BG56" s="85"/>
-      <c r="BH56" s="85"/>
-      <c r="BI56" s="85"/>
-      <c r="BJ56" s="85"/>
-      <c r="BK56" s="85"/>
-      <c r="BL56" s="85"/>
-      <c r="BM56" s="85"/>
-      <c r="BN56" s="85"/>
-      <c r="BO56" s="85"/>
-      <c r="BP56" s="85"/>
-      <c r="BQ56" s="85"/>
+      <c r="BD56" s="105"/>
+      <c r="BE56" s="105"/>
+      <c r="BF56" s="105"/>
+      <c r="BG56" s="105"/>
+      <c r="BH56" s="105"/>
+      <c r="BI56" s="105"/>
+      <c r="BJ56" s="105"/>
+      <c r="BK56" s="105"/>
+      <c r="BL56" s="105"/>
+      <c r="BM56" s="105"/>
+      <c r="BN56" s="105"/>
+      <c r="BO56" s="105"/>
+      <c r="BP56" s="105"/>
+      <c r="BQ56" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="BD52:BE56"/>
-    <mergeCell ref="BF52:BH56"/>
-    <mergeCell ref="BI52:BK56"/>
-    <mergeCell ref="BL52:BN56"/>
-    <mergeCell ref="BO52:BQ56"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:Z5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AG5"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:S5"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AD3:BA3"/>
     <mergeCell ref="A3:B3"/>
@@ -8479,6 +8470,21 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:Z5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AG5"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="BD52:BE56"/>
+    <mergeCell ref="BF52:BH56"/>
+    <mergeCell ref="BI52:BK56"/>
+    <mergeCell ref="BL52:BN56"/>
+    <mergeCell ref="BO52:BQ56"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="F8:AI17">
@@ -8538,20 +8544,20 @@
       <c r="BB1" s="6"/>
     </row>
     <row r="2" spans="1:66" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="A2" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
       <c r="AT2" s="5"/>
       <c r="AU2" s="5"/>
       <c r="AV2" s="5"/>
@@ -8565,39 +8571,39 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="101" t="s">
+      <c r="B3" s="84"/>
+      <c r="C3" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="103">
+      <c r="D3" s="84"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="87">
         <v>1</v>
       </c>
-      <c r="G3" s="104"/>
+      <c r="G3" s="88"/>
       <c r="H3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="105" t="s">
+      <c r="I3" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="106"/>
-      <c r="K3" s="107">
+      <c r="J3" s="90"/>
+      <c r="K3" s="91">
         <v>26</v>
       </c>
-      <c r="L3" s="108"/>
+      <c r="L3" s="92"/>
       <c r="M3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="89" t="s">
+      <c r="N3" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="O3" s="90"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="92"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="95"/>
+      <c r="Q3" s="96"/>
       <c r="R3" s="9" t="s">
         <v>4</v>
       </c>
@@ -8612,32 +8618,32 @@
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
-      <c r="AD3" s="93" t="s">
+      <c r="AD3" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="93"/>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="93"/>
-      <c r="AL3" s="93"/>
-      <c r="AM3" s="93"/>
-      <c r="AN3" s="93"/>
-      <c r="AO3" s="93"/>
-      <c r="AP3" s="93"/>
-      <c r="AQ3" s="93"/>
-      <c r="AR3" s="93"/>
-      <c r="AS3" s="93"/>
-      <c r="AT3" s="93"/>
-      <c r="AU3" s="93"/>
-      <c r="AV3" s="93"/>
-      <c r="AW3" s="93"/>
-      <c r="AX3" s="93"/>
-      <c r="AY3" s="93"/>
-      <c r="AZ3" s="93"/>
-      <c r="BA3" s="93"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="97"/>
+      <c r="AI3" s="97"/>
+      <c r="AJ3" s="97"/>
+      <c r="AK3" s="97"/>
+      <c r="AL3" s="97"/>
+      <c r="AM3" s="97"/>
+      <c r="AN3" s="97"/>
+      <c r="AO3" s="97"/>
+      <c r="AP3" s="97"/>
+      <c r="AQ3" s="97"/>
+      <c r="AR3" s="97"/>
+      <c r="AS3" s="97"/>
+      <c r="AT3" s="97"/>
+      <c r="AU3" s="97"/>
+      <c r="AV3" s="97"/>
+      <c r="AW3" s="97"/>
+      <c r="AX3" s="97"/>
+      <c r="AY3" s="97"/>
+      <c r="AZ3" s="97"/>
+      <c r="BA3" s="97"/>
     </row>
     <row r="4" spans="1:66" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="12"/>
@@ -8691,53 +8697,53 @@
       <c r="BB4" s="15"/>
     </row>
     <row r="5" spans="1:66" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97" t="s">
+      <c r="G5" s="101"/>
+      <c r="H5" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97" t="s">
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97" t="s">
+      <c r="N5" s="101"/>
+      <c r="O5" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97" t="s">
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="97"/>
-      <c r="V5" s="97" t="s">
+      <c r="U5" s="101"/>
+      <c r="V5" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="97"/>
-      <c r="X5" s="97"/>
-      <c r="Y5" s="97"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="86"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="88"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
+      <c r="W5" s="101"/>
+      <c r="X5" s="101"/>
+      <c r="Y5" s="101"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="107"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="107"/>
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="107"/>
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
@@ -10242,7 +10248,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="48"/>
-      <c r="C16" s="52"/>
+      <c r="C16" s="109"/>
       <c r="D16" s="53"/>
       <c r="E16" s="49"/>
       <c r="F16" s="54"/>
@@ -10348,7 +10354,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="48"/>
-      <c r="C17" s="52"/>
+      <c r="C17" s="109"/>
       <c r="D17" s="53"/>
       <c r="E17" s="49"/>
       <c r="F17" s="50"/>
@@ -10453,7 +10459,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="48"/>
-      <c r="C18" s="52"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="53"/>
       <c r="E18" s="49"/>
       <c r="F18" s="50"/>
@@ -10559,7 +10565,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="48"/>
-      <c r="C19" s="52"/>
+      <c r="C19" s="109"/>
       <c r="D19" s="53"/>
       <c r="E19" s="49"/>
       <c r="F19" s="54"/>
@@ -10665,7 +10671,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="48"/>
-      <c r="C20" s="52"/>
+      <c r="C20" s="109"/>
       <c r="D20" s="53"/>
       <c r="E20" s="49"/>
       <c r="F20" s="54"/>
@@ -10771,7 +10777,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="48"/>
-      <c r="C21" s="52"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="53"/>
       <c r="E21" s="49"/>
       <c r="F21" s="54"/>
@@ -10877,7 +10883,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="48"/>
-      <c r="C22" s="52"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="53"/>
       <c r="E22" s="49"/>
       <c r="F22" s="54"/>
@@ -10983,7 +10989,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="48"/>
-      <c r="C23" s="52"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="53"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
@@ -11089,7 +11095,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="48"/>
-      <c r="C24" s="52"/>
+      <c r="C24" s="109"/>
       <c r="D24" s="53"/>
       <c r="E24" s="49"/>
       <c r="F24" s="50"/>
@@ -11198,7 +11204,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="48"/>
-      <c r="C25" s="52"/>
+      <c r="C25" s="109"/>
       <c r="D25" s="53"/>
       <c r="E25" s="49"/>
       <c r="F25" s="54"/>
@@ -11304,7 +11310,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="48"/>
-      <c r="C26" s="52"/>
+      <c r="C26" s="109"/>
       <c r="D26" s="53"/>
       <c r="E26" s="49"/>
       <c r="F26" s="54"/>
@@ -11410,7 +11416,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="48"/>
-      <c r="C27" s="52"/>
+      <c r="C27" s="109"/>
       <c r="D27" s="53"/>
       <c r="E27" s="49"/>
       <c r="F27" s="50"/>
@@ -11519,7 +11525,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="48"/>
-      <c r="C28" s="52"/>
+      <c r="C28" s="109"/>
       <c r="D28" s="53"/>
       <c r="E28" s="49"/>
       <c r="F28" s="54"/>
@@ -11625,7 +11631,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="48"/>
-      <c r="C29" s="52"/>
+      <c r="C29" s="109"/>
       <c r="D29" s="53"/>
       <c r="E29" s="49"/>
       <c r="F29" s="54"/>
@@ -11731,7 +11737,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="48"/>
-      <c r="C30" s="52"/>
+      <c r="C30" s="109"/>
       <c r="D30" s="53"/>
       <c r="E30" s="49"/>
       <c r="F30" s="54"/>
@@ -11837,7 +11843,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="48"/>
-      <c r="C31" s="52"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="53"/>
       <c r="E31" s="49"/>
       <c r="F31" s="54"/>
@@ -11943,7 +11949,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="48"/>
-      <c r="C32" s="52"/>
+      <c r="C32" s="109"/>
       <c r="D32" s="53"/>
       <c r="E32" s="49"/>
       <c r="F32" s="54"/>
@@ -12049,7 +12055,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="48"/>
-      <c r="C33" s="52"/>
+      <c r="C33" s="109"/>
       <c r="D33" s="53"/>
       <c r="E33" s="49"/>
       <c r="F33" s="54"/>
@@ -12155,7 +12161,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="48"/>
-      <c r="C34" s="52"/>
+      <c r="C34" s="109"/>
       <c r="D34" s="53"/>
       <c r="E34" s="49"/>
       <c r="F34" s="54"/>
@@ -12261,7 +12267,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="60"/>
-      <c r="C35" s="61"/>
+      <c r="C35" s="110"/>
       <c r="D35" s="62"/>
       <c r="E35" s="63"/>
       <c r="F35" s="64"/>
@@ -12372,93 +12378,94 @@
       <c r="BC38" s="70"/>
     </row>
     <row r="50" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD50" s="83"/>
-      <c r="BE50" s="83"/>
-      <c r="BF50" s="83"/>
-      <c r="BG50" s="83"/>
-      <c r="BH50" s="83"/>
-      <c r="BI50" s="83"/>
-      <c r="BJ50" s="83"/>
-      <c r="BK50" s="83"/>
-      <c r="BL50" s="83"/>
-      <c r="BM50" s="83"/>
-      <c r="BN50" s="83"/>
-      <c r="BO50" s="83"/>
-      <c r="BP50" s="83"/>
-      <c r="BQ50" s="83"/>
+      <c r="BD50" s="103"/>
+      <c r="BE50" s="103"/>
+      <c r="BF50" s="103"/>
+      <c r="BG50" s="103"/>
+      <c r="BH50" s="103"/>
+      <c r="BI50" s="103"/>
+      <c r="BJ50" s="103"/>
+      <c r="BK50" s="103"/>
+      <c r="BL50" s="103"/>
+      <c r="BM50" s="103"/>
+      <c r="BN50" s="103"/>
+      <c r="BO50" s="103"/>
+      <c r="BP50" s="103"/>
+      <c r="BQ50" s="103"/>
     </row>
     <row r="51" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD51" s="84"/>
-      <c r="BE51" s="84"/>
-      <c r="BF51" s="84"/>
-      <c r="BG51" s="84"/>
-      <c r="BH51" s="84"/>
-      <c r="BI51" s="84"/>
-      <c r="BJ51" s="84"/>
-      <c r="BK51" s="84"/>
-      <c r="BL51" s="84"/>
-      <c r="BM51" s="84"/>
-      <c r="BN51" s="84"/>
-      <c r="BO51" s="84"/>
-      <c r="BP51" s="84"/>
-      <c r="BQ51" s="84"/>
+      <c r="BD51" s="104"/>
+      <c r="BE51" s="104"/>
+      <c r="BF51" s="104"/>
+      <c r="BG51" s="104"/>
+      <c r="BH51" s="104"/>
+      <c r="BI51" s="104"/>
+      <c r="BJ51" s="104"/>
+      <c r="BK51" s="104"/>
+      <c r="BL51" s="104"/>
+      <c r="BM51" s="104"/>
+      <c r="BN51" s="104"/>
+      <c r="BO51" s="104"/>
+      <c r="BP51" s="104"/>
+      <c r="BQ51" s="104"/>
     </row>
     <row r="52" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD52" s="84"/>
-      <c r="BE52" s="84"/>
-      <c r="BF52" s="84"/>
-      <c r="BG52" s="84"/>
-      <c r="BH52" s="84"/>
-      <c r="BI52" s="84"/>
-      <c r="BJ52" s="84"/>
-      <c r="BK52" s="84"/>
-      <c r="BL52" s="84"/>
-      <c r="BM52" s="84"/>
-      <c r="BN52" s="84"/>
-      <c r="BO52" s="84"/>
-      <c r="BP52" s="84"/>
-      <c r="BQ52" s="84"/>
+      <c r="BD52" s="104"/>
+      <c r="BE52" s="104"/>
+      <c r="BF52" s="104"/>
+      <c r="BG52" s="104"/>
+      <c r="BH52" s="104"/>
+      <c r="BI52" s="104"/>
+      <c r="BJ52" s="104"/>
+      <c r="BK52" s="104"/>
+      <c r="BL52" s="104"/>
+      <c r="BM52" s="104"/>
+      <c r="BN52" s="104"/>
+      <c r="BO52" s="104"/>
+      <c r="BP52" s="104"/>
+      <c r="BQ52" s="104"/>
     </row>
     <row r="53" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD53" s="84"/>
-      <c r="BE53" s="84"/>
-      <c r="BF53" s="84"/>
-      <c r="BG53" s="84"/>
-      <c r="BH53" s="84"/>
-      <c r="BI53" s="84"/>
-      <c r="BJ53" s="84"/>
-      <c r="BK53" s="84"/>
-      <c r="BL53" s="84"/>
-      <c r="BM53" s="84"/>
-      <c r="BN53" s="84"/>
-      <c r="BO53" s="84"/>
-      <c r="BP53" s="84"/>
-      <c r="BQ53" s="84"/>
+      <c r="BD53" s="104"/>
+      <c r="BE53" s="104"/>
+      <c r="BF53" s="104"/>
+      <c r="BG53" s="104"/>
+      <c r="BH53" s="104"/>
+      <c r="BI53" s="104"/>
+      <c r="BJ53" s="104"/>
+      <c r="BK53" s="104"/>
+      <c r="BL53" s="104"/>
+      <c r="BM53" s="104"/>
+      <c r="BN53" s="104"/>
+      <c r="BO53" s="104"/>
+      <c r="BP53" s="104"/>
+      <c r="BQ53" s="104"/>
     </row>
     <row r="54" spans="56:69" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BD54" s="85"/>
-      <c r="BE54" s="85"/>
-      <c r="BF54" s="85"/>
-      <c r="BG54" s="85"/>
-      <c r="BH54" s="85"/>
-      <c r="BI54" s="85"/>
-      <c r="BJ54" s="85"/>
-      <c r="BK54" s="85"/>
-      <c r="BL54" s="85"/>
-      <c r="BM54" s="85"/>
-      <c r="BN54" s="85"/>
-      <c r="BO54" s="85"/>
-      <c r="BP54" s="85"/>
-      <c r="BQ54" s="85"/>
+      <c r="BD54" s="105"/>
+      <c r="BE54" s="105"/>
+      <c r="BF54" s="105"/>
+      <c r="BG54" s="105"/>
+      <c r="BH54" s="105"/>
+      <c r="BI54" s="105"/>
+      <c r="BJ54" s="105"/>
+      <c r="BK54" s="105"/>
+      <c r="BL54" s="105"/>
+      <c r="BM54" s="105"/>
+      <c r="BN54" s="105"/>
+      <c r="BO54" s="105"/>
+      <c r="BP54" s="105"/>
+      <c r="BQ54" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="BO50:BQ54"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AG5"/>
+    <mergeCell ref="BD50:BE54"/>
+    <mergeCell ref="BF50:BH54"/>
+    <mergeCell ref="BI50:BK54"/>
+    <mergeCell ref="BL50:BN54"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="AD3:BA3"/>
@@ -12469,13 +12476,12 @@
     <mergeCell ref="O5:S5"/>
     <mergeCell ref="T5:U5"/>
     <mergeCell ref="V5:Z5"/>
-    <mergeCell ref="BO50:BQ54"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AG5"/>
-    <mergeCell ref="BD50:BE54"/>
-    <mergeCell ref="BF50:BH54"/>
-    <mergeCell ref="BI50:BK54"/>
-    <mergeCell ref="BL50:BN54"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="F9:G13">
